--- a/BCA/CA1101 Specifications.xlsx
+++ b/BCA/CA1101 Specifications.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Sr.  No.</t>
   </si>
@@ -104,12 +104,6 @@
     <t>Lab equipments , infrastructure and Software</t>
   </si>
   <si>
-    <t>Python Tutor – for visualizing code flow and memory (variables, loops, function calls)
-VS Code – primary IDE for coding, debugging, and building the Tkinter GUI mini-projects
-Google Colab – cloud-based execution/sharing for quick testing
-GitHub Copilot / Claude – for the Vibe Coding (AI-assisted development) component</t>
-  </si>
-  <si>
     <t>PEP 8 – Style Guide for Python Code (naming, formatting, readability)
 PEP 257 – Docstring Conventions (documentation standards for functions/modules)
 ISO/IEC 25010 – Software Product Quality Model (covers functionality, reliability, usability — relevant to GUI mini-projects)
@@ -126,19 +120,40 @@
 PC6: Debug the code and review the code with appropriate stakeholders.</t>
   </si>
   <si>
+    <t>Python Tutor – for visualizing code flow and memory (variables, loops, function calls)
+VS Code – primary IDE for coding, debugging, 
+Google Colab – cloud-based execution/sharing for quick testing
+GitHub Copilot / Claude – for the Vibe Coding (AI-assisted development) component</t>
+  </si>
+  <si>
+    <t>1. Develop simple Python programs by applying variables, data types, expressions, input-output operations, and control-flow constructs to defined computational tasks.
+2. Process structured data in Python by selecting and using strings, lists, tuples, sets, dictionaries, functions, and basic modules appropriately.
+3. Construct object-oriented Python applications using classes and objects to represent and process requirements of simple real-world problem scenarios.
+4. Manage persistent program data and expected execution errors through file operations and exception-handling mechanisms.
+5. Test and debug Python programs by creating relevant test cases, identifying logical or runtime defects, and correcting code to meet stated specifications.</t>
+  </si>
+  <si>
+    <t>1. Develop Python programs using variables, data types, expressions, input-output operations, conditional statements, and iterative constructs to solve defined computational problems.
+2. Construct Python solutions using strings, lists, tuples, sets, dictionaries, functions, and basic modules for structured data-processing tasks.
+3. Develop object-oriented Python programs using classes and objects to model and implement simple application requirements.
+4. Implement file-handling and exception-handling mechanisms in Python programs to process stored data and manage execution errors appropriately.
+5. Test and debug Python programs using suitable test cases to identify, correct, and verify logical and runtime errors.</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-File handling
-Object Oriented Programming
-Version control expectation – whether students are expected to maintain GitHub repos for mini-projects
-Vibe Coding scope – clarify how much AI-assistance is expected/allowed (e.g., students may use AI tools to assist coding but must be able to explain and debug the generated code)
-Numpy and Pandas should be covered</t>
+1. File handling
+2. Object Oriented Programming
+3. Version control expectation – whether students are expected to maintain GitHub repos for mini-projects
+4. Vibe Coding scope – clarify how much AI-assistance is expected/allowed (e.g., students may use AI tools to assist coding but must be able to explain and debug the generated code)
+5. Numpy and Pandas should be covered
+6. GUI designing will not be covered in the syllabus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -147,11 +162,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
@@ -251,20 +261,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -273,8 +280,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,13 +574,13 @@
       <c r="P1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -575,53 +588,59 @@
       <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="8">
         <v>1</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="8">
         <v>4</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <v>90</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="J2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="9" t="s">
-        <v>17</v>
+      <c r="L2" s="8" t="s">
+        <v>19</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="9" t="s">
-        <v>19</v>
+      <c r="Q2" s="9" t="s">
+        <v>33</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>7</v>
+      <c r="R2" s="8" t="s">
+        <v>31</v>
       </c>
-      <c r="N2" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>31</v>
+      <c r="S2" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
